--- a/artfynd/A 47612-2022 artfynd.xlsx
+++ b/artfynd/A 47612-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47612-2022 artfynd.xlsx
+++ b/artfynd/A 47612-2022 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>104438489</v>
       </c>
       <c r="B2" t="n">
-        <v>56717</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58286</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>439098.3519520856</v>
+        <v>439099</v>
       </c>
       <c r="R2" t="n">
-        <v>6257077.295859897</v>
+        <v>6257077</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -762,19 +757,9 @@
           <t>2022-05-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-05-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
